--- a/БД подпрограмм-статей.xlsx
+++ b/БД подпрограмм-статей.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13440"/>
+    <workbookView windowWidth="30720" windowHeight="12720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Название модели</t>
   </si>
@@ -41,10 +41,16 @@
     <t>TITAN_A1</t>
   </si>
   <si>
-    <t>Посчитать мою модель с флюидными пикапами (9 сортов водорода) и модель с флюидными пикапами Bera (3 сорта водорода).</t>
+    <t>Посчитать мою модель с флюидными пикапами (9 сортов водорода).</t>
   </si>
   <si>
     <t>Я предполагаю, что роль пикапов у Bera переоценена. Я думаю, что так происходит из-за малого количества сортов атомов.</t>
+  </si>
+  <si>
+    <t>TITAN_A2</t>
+  </si>
+  <si>
+    <t>Посчитать мою модель без пикапов но с подходом Bera (3 сорта водорода).</t>
   </si>
 </sst>
 </file>
@@ -57,7 +63,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,13 +81,6 @@
     <font>
       <b/>
       <sz val="22"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -550,148 +549,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1056,9 +1055,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+    <row r="3" ht="65" customHeight="1" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:3">
